--- a/data/trans_orig/P6709-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>29161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45115</t>
+          <t>43762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30387</t>
+          <t>29569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49621</t>
+          <t>49159</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80727</t>
+          <t>80713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40311</t>
+          <t>42342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74394</t>
+          <t>73372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101690</t>
+          <t>102371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55378</t>
+          <t>56634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79867</t>
+          <t>80362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137228</t>
+          <t>137396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173532</t>
+          <t>174231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56152</t>
+          <t>57263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93362</t>
+          <t>93271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>40472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69005</t>
+          <t>68819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105410</t>
+          <t>107284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151955</t>
+          <t>148951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>54683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90071</t>
+          <t>90809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60722</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96227</t>
+          <t>94642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141309</t>
+          <t>139757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166429</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215500</t>
+          <t>218969</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100125</t>
+          <t>99342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143369</t>
+          <t>140388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278513</t>
+          <t>276149</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>343372</t>
+          <t>341475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219632</t>
+          <t>220097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274000</t>
+          <t>273446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113893</t>
+          <t>113591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154375</t>
+          <t>155501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>345528</t>
+          <t>346508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411631</t>
+          <t>414406</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297758</t>
+          <t>296518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359035</t>
+          <t>358246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190485</t>
+          <t>192168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>238273</t>
+          <t>238983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>507369</t>
+          <t>501874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>585391</t>
+          <t>579788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21724</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28780</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43615</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>25401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>22448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50180</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80719</t>
+          <t>79869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71289</t>
+          <t>69897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98186</t>
+          <t>100958</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142157</t>
+          <t>139713</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>62859</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95200</t>
+          <t>95831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44034</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69695</t>
+          <t>73086</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114101</t>
+          <t>113901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157046</t>
+          <t>157360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129906</t>
+          <t>129613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168379</t>
+          <t>167137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76737</t>
+          <t>75931</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107980</t>
+          <t>105818</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>214304</t>
+          <t>214587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>265031</t>
+          <t>263041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79572</t>
+          <t>77017</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122147</t>
+          <t>117614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74772</t>
+          <t>72147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110300</t>
+          <t>112027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>160681</t>
+          <t>164148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>217614</t>
+          <t>216175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81808</t>
+          <t>80178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120988</t>
+          <t>121985</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53269</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88085</t>
+          <t>86180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>142173</t>
+          <t>142914</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>191375</t>
+          <t>196682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>265983</t>
+          <t>264221</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>327933</t>
+          <t>326447</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172071</t>
+          <t>171579</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>225137</t>
+          <t>222802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>452950</t>
+          <t>452779</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>531319</t>
+          <t>529543</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>319883</t>
+          <t>322827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>387266</t>
+          <t>386931</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183167</t>
+          <t>183022</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>236674</t>
+          <t>233338</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>518770</t>
+          <t>520371</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>604236</t>
+          <t>607523</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>527815</t>
+          <t>525589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>600010</t>
+          <t>602175</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>342086</t>
+          <t>343672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>403237</t>
+          <t>406793</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>890615</t>
+          <t>888407</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>991452</t>
+          <t>985270</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>38064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31482</t>
+          <t>31884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55921</t>
+          <t>56237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45340</t>
+          <t>44372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35093</t>
+          <t>35699</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>31099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53378</t>
+          <t>53400</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36882</t>
+          <t>37935</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49196</t>
+          <t>49285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55288</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>49006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>74667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86214</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128225</t>
+          <t>127516</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49767</t>
+          <t>49859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80436</t>
+          <t>78805</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146703</t>
+          <t>142526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196292</t>
+          <t>192606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105432</t>
+          <t>107888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84992</t>
+          <t>84978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123382</t>
+          <t>124301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204103</t>
+          <t>202323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262381</t>
+          <t>260929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>231017</t>
+          <t>229344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>290351</t>
+          <t>284745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155693</t>
+          <t>157409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>200931</t>
+          <t>201995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>403340</t>
+          <t>400424</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>476310</t>
+          <t>473204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>188658</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241104</t>
+          <t>234539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>126519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165698</t>
+          <t>167522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323480</t>
+          <t>326517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391427</t>
+          <t>394028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193748</t>
+          <t>197231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>247785</t>
+          <t>250369</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137141</t>
+          <t>138627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183154</t>
+          <t>183151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347417</t>
+          <t>347462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416480</t>
+          <t>415532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>30673</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46213</t>
+          <t>43941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67976</t>
+          <t>69228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55690</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>45999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58768</t>
+          <t>58300</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93038</t>
+          <t>92233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73935</t>
+          <t>72210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107951</t>
+          <t>109540</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54299</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82930</t>
+          <t>83242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136764</t>
+          <t>135535</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>180149</t>
+          <t>181303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67106</t>
+          <t>67181</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99330</t>
+          <t>99819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63627</t>
+          <t>63183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92931</t>
+          <t>91450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137698</t>
+          <t>139074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181314</t>
+          <t>185191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96927</t>
+          <t>98107</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134723</t>
+          <t>134456</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82655</t>
+          <t>82768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115174</t>
+          <t>116232</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>190593</t>
+          <t>189595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>243134</t>
+          <t>241138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131196</t>
+          <t>130285</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179320</t>
+          <t>179110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91850</t>
+          <t>92661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131484</t>
+          <t>132424</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>234139</t>
+          <t>233721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>296636</t>
+          <t>297626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163832</t>
+          <t>162168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216839</t>
+          <t>216267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128476</t>
+          <t>129307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>173724</t>
+          <t>177117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>305742</t>
+          <t>305316</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>373563</t>
+          <t>370818</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>340301</t>
+          <t>342530</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>410102</t>
+          <t>411635</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>235192</t>
+          <t>238104</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>291343</t>
+          <t>294435</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>590013</t>
+          <t>597459</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>685415</t>
+          <t>685681</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>289868</t>
+          <t>289585</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>355778</t>
+          <t>352874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>206361</t>
+          <t>208384</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>259641</t>
+          <t>265542</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>515833</t>
+          <t>514549</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>597302</t>
+          <t>594914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>347318</t>
+          <t>351096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>414275</t>
+          <t>421676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>247660</t>
+          <t>245734</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>305484</t>
+          <t>305945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>610586</t>
+          <t>611676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>702414</t>
+          <t>705095</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6709-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43762</t>
+          <t>42828</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32696</t>
+          <t>34377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>29961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>53347</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49159</t>
+          <t>48714</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80713</t>
+          <t>78128</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20806</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42342</t>
+          <t>41469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>29724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65385</t>
+          <t>66347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73372</t>
+          <t>74072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102371</t>
+          <t>100068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56634</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80362</t>
+          <t>81206</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137396</t>
+          <t>138913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>174231</t>
+          <t>176013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57263</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93271</t>
+          <t>94123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>40567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68819</t>
+          <t>67992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107284</t>
+          <t>105519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148951</t>
+          <t>151954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90809</t>
+          <t>90999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32351</t>
+          <t>33803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>61041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94642</t>
+          <t>96513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139757</t>
+          <t>138942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168484</t>
+          <t>168893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218969</t>
+          <t>217599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99342</t>
+          <t>99544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140388</t>
+          <t>140439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>276149</t>
+          <t>276758</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>341475</t>
+          <t>344253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220097</t>
+          <t>219228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273446</t>
+          <t>272700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113591</t>
+          <t>113425</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155501</t>
+          <t>152703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>346508</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414406</t>
+          <t>413740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296518</t>
+          <t>297892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358246</t>
+          <t>357262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192168</t>
+          <t>192932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>238983</t>
+          <t>238912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>501874</t>
+          <t>502226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>580189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>29450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>20597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42370</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>42205</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48749</t>
+          <t>49417</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79869</t>
+          <t>78463</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>41949</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69897</t>
+          <t>70158</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100958</t>
+          <t>101242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139713</t>
+          <t>141735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62859</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95831</t>
+          <t>96422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45017</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73086</t>
+          <t>71328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113901</t>
+          <t>114525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157360</t>
+          <t>157191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129613</t>
+          <t>127678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167137</t>
+          <t>166214</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75931</t>
+          <t>74727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105818</t>
+          <t>107038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>214587</t>
+          <t>214211</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263041</t>
+          <t>263149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77017</t>
+          <t>78092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117614</t>
+          <t>120887</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72147</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112027</t>
+          <t>110537</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164148</t>
+          <t>163155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216175</t>
+          <t>217905</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80178</t>
+          <t>82441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121985</t>
+          <t>120302</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53343</t>
+          <t>53761</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>86180</t>
+          <t>85279</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>142914</t>
+          <t>139488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>196682</t>
+          <t>192678</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>264221</t>
+          <t>267195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>326447</t>
+          <t>327040</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171579</t>
+          <t>170711</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>222802</t>
+          <t>223715</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>452779</t>
+          <t>451928</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>529543</t>
+          <t>532398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322827</t>
+          <t>321339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>386931</t>
+          <t>387059</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183022</t>
+          <t>186562</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>233338</t>
+          <t>239986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>520371</t>
+          <t>524867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>607523</t>
+          <t>605816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>525589</t>
+          <t>524947</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>602175</t>
+          <t>596997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>343672</t>
+          <t>343148</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>406793</t>
+          <t>404531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>888407</t>
+          <t>888202</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>985270</t>
+          <t>984220</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38064</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>31421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>54361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>30242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44372</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16414</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>32084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53400</t>
+          <t>55084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>36945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>32279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55285</t>
+          <t>54767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49006</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74667</t>
+          <t>74603</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86738</t>
+          <t>86443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127516</t>
+          <t>127589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49859</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>79556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142526</t>
+          <t>144877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192606</t>
+          <t>196066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107888</t>
+          <t>105158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149330</t>
+          <t>147439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84978</t>
+          <t>86677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124301</t>
+          <t>126664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202323</t>
+          <t>202234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260929</t>
+          <t>258361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>229344</t>
+          <t>230943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>284745</t>
+          <t>287269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157409</t>
+          <t>157434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>201995</t>
+          <t>202061</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>400424</t>
+          <t>403435</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473204</t>
+          <t>472951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>186710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234539</t>
+          <t>237181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126519</t>
+          <t>127664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167522</t>
+          <t>168096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>326517</t>
+          <t>326461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394028</t>
+          <t>394829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197231</t>
+          <t>196440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250369</t>
+          <t>249550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138627</t>
+          <t>137499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183151</t>
+          <t>181124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347462</t>
+          <t>346229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>415532</t>
+          <t>416540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30673</t>
+          <t>31057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>22107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43941</t>
+          <t>45429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>39524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69228</t>
+          <t>68431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29944</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55264</t>
+          <t>55005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45999</t>
+          <t>45676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58300</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92233</t>
+          <t>90973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72210</t>
+          <t>75060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109540</t>
+          <t>109043</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54586</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83242</t>
+          <t>82070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135535</t>
+          <t>137454</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>181303</t>
+          <t>181697</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67181</t>
+          <t>67555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99819</t>
+          <t>102048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63183</t>
+          <t>62062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91450</t>
+          <t>92064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139074</t>
+          <t>136993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185191</t>
+          <t>182937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98107</t>
+          <t>99623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134456</t>
+          <t>136159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82768</t>
+          <t>82233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116232</t>
+          <t>116609</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189595</t>
+          <t>190219</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241138</t>
+          <t>238859</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130285</t>
+          <t>129927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179110</t>
+          <t>178431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92661</t>
+          <t>90054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132424</t>
+          <t>129898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233721</t>
+          <t>230956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>297626</t>
+          <t>297836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162168</t>
+          <t>163930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216267</t>
+          <t>218101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129307</t>
+          <t>128387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>177117</t>
+          <t>173088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>305316</t>
+          <t>305049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>370818</t>
+          <t>374963</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>342530</t>
+          <t>339714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>411635</t>
+          <t>408247</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>238104</t>
+          <t>236222</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>294435</t>
+          <t>291515</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>597459</t>
+          <t>594998</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>685681</t>
+          <t>681619</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>289585</t>
+          <t>290437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>352874</t>
+          <t>355559</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>208384</t>
+          <t>209122</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>265542</t>
+          <t>262007</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>514549</t>
+          <t>515473</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>594914</t>
+          <t>600859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>351096</t>
+          <t>348064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>421676</t>
+          <t>415836</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,82 +6203,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>275050</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>248725</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>305893</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>656559</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>606681</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>699629</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>26,77%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>24,74%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>275050</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>245734</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>305945</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>29,61%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>656559</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>611676</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>705095</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>24,94%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
